--- a/gte/nodes/HPT/turbine_blade_parameters.xlsx
+++ b/gte/nodes/HPT/turbine_blade_parameters.xlsx
@@ -809,124 +809,124 @@
         <v>89</v>
       </c>
       <c r="D3">
-        <v>78.0930567291021</v>
+        <v>78.0740537413631</v>
       </c>
       <c r="E3">
-        <v>70.65710180297593</v>
+        <v>70.640879388149486</v>
       </c>
       <c r="F3">
-        <v>52.0330716995944</v>
+        <v>52.00542832232891</v>
       </c>
       <c r="G3">
-        <v>44.280952217527471</v>
+        <v>44.259371178132405</v>
       </c>
       <c r="H3">
-        <v>474.06987630185256</v>
+        <v>473.86551064294986</v>
       </c>
       <c r="I3">
-        <v>171.20607131219583</v>
+        <v>171.13965032386037</v>
       </c>
       <c r="J3">
-        <v>4235.7375255172892</v>
+        <v>4232.2188802981427</v>
       </c>
       <c r="K3">
-        <v>1714.5172968245583</v>
+        <v>1711.6033260170107</v>
       </c>
       <c r="L3">
-        <v>13572.251481999638</v>
+        <v>13563.476183335128</v>
       </c>
       <c r="M3">
-        <v>2766.8669096288622</v>
+        <v>2765.2569181644571</v>
       </c>
       <c r="N3">
-        <v>28.629221472316949</v>
+        <v>28.623049955528398</v>
       </c>
       <c r="O3">
-        <v>16.161032657442711</v>
+        <v>16.157897441835104</v>
       </c>
       <c r="P3">
-        <v>8.9348379579812924</v>
+        <v>8.9312659082442742</v>
       </c>
       <c r="Q3">
-        <v>10.014348695018649</v>
+        <v>10.001208502985811</v>
       </c>
       <c r="R3">
-        <v>44317.649295783143</v>
+        <v>44264.309456557043</v>
       </c>
       <c r="S3">
-        <v>18828.2945714</v>
+        <v>18773.609281615</v>
       </c>
       <c r="T3">
-        <v>509156.28399035922</v>
+        <v>508717.39665980468</v>
       </c>
       <c r="U3">
-        <v>58593.177332556159</v>
+        <v>58547.722614916034</v>
       </c>
       <c r="V3">
-        <v>128682.776957136</v>
+        <v>128548.2978506661</v>
       </c>
       <c r="W3">
-        <v>29176.522809067283</v>
+        <v>29121.908394489285</v>
       </c>
       <c r="X3">
-        <v>6472.0208727455156</v>
+        <v>6465.2372547224877</v>
       </c>
       <c r="Y3">
-        <v>1658.520517358081</v>
+        <v>1655.5075437148682</v>
       </c>
       <c r="Z3">
-        <v>120593.2904342097</v>
+        <v>120489.34029358366</v>
       </c>
       <c r="AA3">
-        <v>13877.750847246525</v>
+        <v>13866.984930889716</v>
       </c>
       <c r="AB3">
-        <v>7416.9092404978146</v>
+        <v>7409.2854171619165</v>
       </c>
       <c r="AC3">
-        <v>1468.1527833352027</v>
+        <v>1465.9973916025633</v>
       </c>
       <c r="AD3">
-        <v>3.702975538147343</v>
+        <v>3.7023287925477355</v>
       </c>
       <c r="AE3">
-        <v>6.7560467245308145</v>
+        <v>6.75061762590563</v>
       </c>
       <c r="AF3">
-        <v>5992.0040733827327</v>
+        <v>5985.7978485632621</v>
       </c>
       <c r="AG3">
-        <v>1484.5960700350806</v>
+        <v>1481.979293895906</v>
       </c>
       <c r="AH3">
-        <v>121073.30723357247</v>
+        <v>120968.77969974287</v>
       </c>
       <c r="AI3">
-        <v>14051.675294569524</v>
+        <v>14040.51318070868</v>
       </c>
       <c r="AJ3">
-        <v>-1.1581153797917651E-12</v>
+        <v>-1.1571170965858158E-12</v>
       </c>
       <c r="AK3">
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>127065.31130695521</v>
+        <v>126954.57754830612</v>
       </c>
       <c r="AM3">
-        <v>15536.271364604605</v>
+        <v>15522.492474604584</v>
       </c>
       <c r="AN3">
-        <v>3148.4546585183684</v>
+        <v>3146.4175424759178</v>
       </c>
       <c r="AO3">
-        <v>637.5351834070824</v>
+        <v>637.21364616718654</v>
       </c>
       <c r="AP3">
-        <v>23.795012224292822</v>
+        <v>23.789882803726211</v>
       </c>
       <c r="AQ3">
-        <v>13.432149037405283</v>
+        <v>13.42954322104451</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1410,124 +1410,124 @@
         <v>89</v>
       </c>
       <c r="D3">
-        <v>78.0930567291021</v>
+        <v>78.0740537413631</v>
       </c>
       <c r="E3">
-        <v>70.65710180297593</v>
+        <v>70.640879388149486</v>
       </c>
       <c r="F3">
-        <v>44.793138898860846</v>
+        <v>44.784601656943025</v>
       </c>
       <c r="G3">
-        <v>39.560413972905636</v>
+        <v>39.552861606610783</v>
       </c>
       <c r="H3">
-        <v>474.06987630185256</v>
+        <v>473.86551064294986</v>
       </c>
       <c r="I3">
-        <v>103.99962177835239</v>
+        <v>103.95927415742942</v>
       </c>
       <c r="J3">
-        <v>4235.7375255172892</v>
+        <v>4232.2188802981427</v>
       </c>
       <c r="K3">
-        <v>883.76131995231424</v>
+        <v>883.25728393682414</v>
       </c>
       <c r="L3">
-        <v>13572.251481999638</v>
+        <v>13563.476183335128</v>
       </c>
       <c r="M3">
-        <v>1497.993577709773</v>
+        <v>1497.1219214456262</v>
       </c>
       <c r="N3">
-        <v>28.629221472316949</v>
+        <v>28.623049955528398</v>
       </c>
       <c r="O3">
-        <v>14.403836784160129</v>
+        <v>14.401042461863272</v>
       </c>
       <c r="P3">
-        <v>8.9348379579812924</v>
+        <v>8.9312659082442742</v>
       </c>
       <c r="Q3">
-        <v>8.4977359036537372</v>
+        <v>8.4961855601191925</v>
       </c>
       <c r="R3">
-        <v>44317.649295783143</v>
+        <v>44264.309456557043</v>
       </c>
       <c r="S3">
-        <v>8189.7654210607416</v>
+        <v>8183.5940690228272</v>
       </c>
       <c r="T3">
-        <v>509156.28399035922</v>
+        <v>508717.39665980468</v>
       </c>
       <c r="U3">
-        <v>28273.38550682156</v>
+        <v>28251.45191636878</v>
       </c>
       <c r="V3">
-        <v>128682.776957136</v>
+        <v>128548.2978506661</v>
       </c>
       <c r="W3">
-        <v>13416.179043801674</v>
+        <v>13405.923410746953</v>
       </c>
       <c r="X3">
-        <v>6472.0208727455156</v>
+        <v>6465.2372547224877</v>
       </c>
       <c r="Y3">
-        <v>679.79512224154189</v>
+        <v>679.27628736868439</v>
       </c>
       <c r="Z3">
-        <v>120593.2904342097</v>
+        <v>120489.34029358366</v>
       </c>
       <c r="AA3">
-        <v>6696.5305097698947</v>
+        <v>6691.3355550439892</v>
       </c>
       <c r="AB3">
-        <v>7416.9092404978146</v>
+        <v>7409.2854171619165</v>
       </c>
       <c r="AC3">
-        <v>686.62523505461991</v>
+        <v>686.09776002272383</v>
       </c>
       <c r="AD3">
-        <v>3.702975538147343</v>
+        <v>3.7023287925477355</v>
       </c>
       <c r="AE3">
-        <v>6.4284351206741626</v>
+        <v>6.4284909212768566</v>
       </c>
       <c r="AF3">
-        <v>5992.0040733827327</v>
+        <v>5985.7978485632621</v>
       </c>
       <c r="AG3">
-        <v>602.43269263170532</v>
+        <v>601.97261197453577</v>
       </c>
       <c r="AH3">
-        <v>121073.30723357247</v>
+        <v>120968.77969974287</v>
       </c>
       <c r="AI3">
-        <v>6773.89293937973</v>
+        <v>6768.6392304381379</v>
       </c>
       <c r="AJ3">
-        <v>-1.1581153797917651E-12</v>
+        <v>-1.1571170965858158E-12</v>
       </c>
       <c r="AK3">
-        <v>1.4840770124016935E-13</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>127065.31130695521</v>
+        <v>126954.57754830612</v>
       </c>
       <c r="AM3">
-        <v>7376.3256320114369</v>
+        <v>7370.6118424126735</v>
       </c>
       <c r="AN3">
-        <v>3148.4546585183684</v>
+        <v>3146.4175424759178</v>
       </c>
       <c r="AO3">
-        <v>342.33107579067223</v>
+        <v>342.13166013274713</v>
       </c>
       <c r="AP3">
-        <v>23.795012224292822</v>
+        <v>23.789882803726211</v>
       </c>
       <c r="AQ3">
-        <v>11.971665827071861</v>
+        <v>11.96934334221922</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2011,124 +2011,124 @@
         <v>89</v>
       </c>
       <c r="D3">
-        <v>78.0930567291021</v>
+        <v>78.0740537413631</v>
       </c>
       <c r="E3">
-        <v>70.65710180297593</v>
+        <v>70.640879388149486</v>
       </c>
       <c r="F3">
-        <v>40.207418296872056</v>
+        <v>40.209005880849716</v>
       </c>
       <c r="G3">
-        <v>36.205390768988053</v>
+        <v>36.206082022156089</v>
       </c>
       <c r="H3">
-        <v>474.06987630185256</v>
+        <v>473.86551064294986</v>
       </c>
       <c r="I3">
-        <v>74.307983959854383</v>
+        <v>74.279155486085955</v>
       </c>
       <c r="J3">
-        <v>4235.7375255172892</v>
+        <v>4232.2188802981427</v>
       </c>
       <c r="K3">
-        <v>554.09042442276689</v>
+        <v>554.2208196676778</v>
       </c>
       <c r="L3">
-        <v>13572.251481999638</v>
+        <v>13563.476183335128</v>
       </c>
       <c r="M3">
-        <v>983.53736411899627</v>
+        <v>982.96506092810523</v>
       </c>
       <c r="N3">
-        <v>28.629221472316949</v>
+        <v>28.623049955528398</v>
       </c>
       <c r="O3">
-        <v>13.235958125984981</v>
+        <v>13.233390370360835</v>
       </c>
       <c r="P3">
-        <v>8.9348379579812924</v>
+        <v>8.9312659082442742</v>
       </c>
       <c r="Q3">
-        <v>7.45667416736968</v>
+        <v>7.4613236518486659</v>
       </c>
       <c r="R3">
-        <v>44317.649295783143</v>
+        <v>44264.309456557043</v>
       </c>
       <c r="S3">
-        <v>4501.1526447432625</v>
+        <v>4504.7725218109972</v>
       </c>
       <c r="T3">
-        <v>509156.28399035922</v>
+        <v>508717.39665980468</v>
       </c>
       <c r="U3">
-        <v>17058.306740213251</v>
+        <v>17045.07345006596</v>
       </c>
       <c r="V3">
-        <v>128682.776957136</v>
+        <v>128548.2978506661</v>
       </c>
       <c r="W3">
-        <v>7735.5869755433923</v>
+        <v>7735.8025570114887</v>
       </c>
       <c r="X3">
-        <v>6472.0208727455156</v>
+        <v>6465.2372547224877</v>
       </c>
       <c r="Y3">
-        <v>369.48089056311488</v>
+        <v>369.55161167759906</v>
       </c>
       <c r="Z3">
-        <v>120593.2904342097</v>
+        <v>120489.34029358366</v>
       </c>
       <c r="AA3">
-        <v>4040.247373392574</v>
+        <v>4037.1130783788221</v>
       </c>
       <c r="AB3">
-        <v>7416.9092404978146</v>
+        <v>7409.2854171619165</v>
       </c>
       <c r="AC3">
-        <v>401.66931987440682</v>
+        <v>401.58209896775321</v>
       </c>
       <c r="AD3">
-        <v>3.702975538147343</v>
+        <v>3.7023287925477355</v>
       </c>
       <c r="AE3">
-        <v>6.17221345957636</v>
+        <v>6.1761414402417945</v>
       </c>
       <c r="AF3">
-        <v>5992.0040733827327</v>
+        <v>5985.7978485632621</v>
       </c>
       <c r="AG3">
-        <v>326.04272338297534</v>
+        <v>326.09502379808629</v>
       </c>
       <c r="AH3">
-        <v>121073.30723357247</v>
+        <v>120968.77969974287</v>
       </c>
       <c r="AI3">
-        <v>4083.6855405727129</v>
+        <v>4080.5696662583346</v>
       </c>
       <c r="AJ3">
-        <v>-1.1581153797917651E-12</v>
+        <v>-1.1571170965858158E-12</v>
       </c>
       <c r="AK3">
-        <v>-5.2909689681004678E-14</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>127065.31130695521</v>
+        <v>126954.57754830612</v>
       </c>
       <c r="AM3">
-        <v>4409.7282639556888</v>
+        <v>4406.66469005642</v>
       </c>
       <c r="AN3">
-        <v>3148.4546585183684</v>
+        <v>3146.4175424759178</v>
       </c>
       <c r="AO3">
-        <v>224.25294420828763</v>
+        <v>224.114271244821</v>
       </c>
       <c r="AP3">
-        <v>23.795012224292822</v>
+        <v>23.789882803726211</v>
       </c>
       <c r="AQ3">
-        <v>11.00099021947144</v>
+        <v>10.998856044201443</v>
       </c>
       <c r="AR3">
         <v>0</v>
